--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -1717,7 +1717,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -649,7 +649,7 @@
     <t>MedicationStatement.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -682,7 +682,7 @@
     <t>MedicationStatement.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -712,7 +712,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -894,7 +894,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -910,7 +910,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -941,7 +941,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1014,7 +1014,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1055,7 +1055,7 @@
     <t>MedicationStatement.dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1099,7 +1099,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1115,7 +1115,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1131,7 +1131,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1239,7 +1239,7 @@
     <t>補足指示はコード化されるように意図されているが、コードがない場合はエレメントはテキストだけで表現することができる。たとえば、「大量の水で服用する」という指示はコード化されていることもあれば、されていないことおある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.additionalInstruction</t>
@@ -1266,7 +1266,7 @@
     <t>MedicationStatement.dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1626,7 +1626,7 @@
 【JP Core仕様】頓用指示時にはJAMI処方・注射オーダ標準用法規格の表6 イベント区分、イベント詳細区分(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionJAMI_CS”)を推奨するが、MERIT-9 処方オーダ 表5 頓用指示(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionMERIT9_CS”) を使用してもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS|1.1.0a</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -1677,7 +1677,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -1701,7 +1701,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1749,7 +1749,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1773,7 +1773,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1804,7 +1804,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1828,7 +1828,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1863,7 +1863,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.method.coding:unitDigit1.id</t>
@@ -2019,7 +2019,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.method.coding:unitDigit2.id</t>
@@ -2085,7 +2085,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.type</t>
@@ -2097,7 +2097,7 @@
     <t>MedicationStatement.dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -2121,7 +2121,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -2158,7 +2158,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -2168,7 +2168,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2552,7 +2552,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2567,7 +2567,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -649,7 +649,7 @@
     <t>MedicationStatement.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
 </t>
   </si>
   <si>
@@ -682,7 +682,7 @@
     <t>MedicationStatement.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -712,7 +712,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -894,7 +894,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
 </t>
   </si>
   <si>
@@ -910,7 +910,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -941,7 +941,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1014,7 +1014,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -1055,7 +1055,7 @@
     <t>MedicationStatement.dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection|1.3.0-dev}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage_Injection}
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
 </t>
   </si>
   <si>
@@ -1099,7 +1099,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
 </t>
   </si>
   <si>
@@ -1115,7 +1115,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
 </t>
   </si>
   <si>
@@ -1131,7 +1131,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
 </t>
   </si>
   <si>
@@ -1239,7 +1239,7 @@
     <t>補足指示はコード化されるように意図されているが、コードがない場合はエレメントはテキストだけで表現することができる。たとえば、「大量の水で服用する」という指示はコード化されていることもあれば、されていないことおある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageJAMIAdditional_VS</t>
   </si>
   <si>
     <t>Dosage.additionalInstruction</t>
@@ -1266,7 +1266,7 @@
     <t>MedicationStatement.dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming|1.3.0-dev}
+    <t xml:space="preserve">Timing {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationTiming}
 </t>
   </si>
   <si>
@@ -1626,7 +1626,7 @@
 【JP Core仕様】頓用指示時にはJAMI処方・注射オーダ標準用法規格の表6 イベント区分、イベント詳細区分(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionJAMI_CS”)を推奨するが、MERIT-9 処方オーダ 表5 頓用指示(“http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicationAsNeededConditionMERIT9_CS”) を使用してもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUsageInjection_VS</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -1677,7 +1677,7 @@
     <t>薬が最初に体に入る解剖学的部位のコード化された仕様。 / A coded specification of the anatomic site where the medication first enters the body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -1701,7 +1701,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
 </t>
   </si>
   <si>
@@ -1749,7 +1749,7 @@
     <t>患者の体への、または患者の体内への治療剤の投与のルートまたは生理学的経路を指定するコード。 / A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1773,7 +1773,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
 </t>
   </si>
   <si>
@@ -1804,7 +1804,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1828,7 +1828,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
 </t>
   </si>
   <si>
@@ -1863,7 +1863,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.method.coding:unitDigit1.id</t>
@@ -2019,7 +2019,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.method.coding:unitDigit2.id</t>
@@ -2085,7 +2085,7 @@
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationIngredientStrengthStrengthType_VS</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.type</t>
@@ -2097,7 +2097,7 @@
     <t>MedicationStatement.dosage.doseAndRate.dose[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -2121,7 +2121,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity|4.0.1}</t>
+RangeQuantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>
@@ -2158,7 +2158,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -2168,7 +2168,7 @@
     <t>rateRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime|1.3.0-dev}
+    <t xml:space="preserve">Range {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRange_UnitOfTime}
 </t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -2552,7 +2552,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2567,7 +2567,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
